--- a/security-tests/backend_security_report.xlsx
+++ b/security-tests/backend_security_report.xlsx
@@ -416,7 +416,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>1/8/2026, 9:10:34 am</v>
+        <v>1/8/2026, 11:02:05 am</v>
       </c>
     </row>
     <row r="3">
